--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_pair_profile_summary.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/data/D4_pair_profile_summary.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3.367710252973697</v>
+        <v>3.394775810721377</v>
       </c>
       <c r="F2" t="n">
         <v>3.4</v>
@@ -546,10 +546,10 @@
         <v>1.75</v>
       </c>
       <c r="H2" t="n">
-        <v>3.367741327300151</v>
+        <v>3.395028550148957</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9751674562979905</v>
+        <v>0.9874203561509557</v>
       </c>
       <c r="J2" t="n">
         <v>0.2465283450416599</v>
@@ -558,22 +558,22 @@
         <v>0.002940695964711648</v>
       </c>
       <c r="L2" t="n">
-        <v>3.699885639601372</v>
+        <v>3.793007678483908</v>
       </c>
       <c r="M2" t="n">
-        <v>4.034308119588302</v>
+        <v>4.056853455317759</v>
       </c>
       <c r="N2" t="n">
-        <v>4.136415618363013</v>
+        <v>4.103414474759027</v>
       </c>
       <c r="O2" t="n">
         <v>2.771932690736808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3141229686714693</v>
+        <v>0.2908669755129054</v>
       </c>
       <c r="Q2" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3.391024156187955</v>
+        <v>3.421027708850289</v>
       </c>
       <c r="F3" t="n">
         <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0125</v>
+        <v>2.125</v>
       </c>
       <c r="H3" t="n">
-        <v>3.39073361469712</v>
+        <v>3.420809200728115</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9874203561509557</v>
+        <v>0.9875837281489953</v>
       </c>
       <c r="J3" t="n">
         <v>0.006534879921581441</v>
@@ -619,22 +619,22 @@
         <v>0.00326743996079072</v>
       </c>
       <c r="L3" t="n">
-        <v>4.109785982682568</v>
+        <v>4.20094755758863</v>
       </c>
       <c r="M3" t="n">
-        <v>4.019768011762784</v>
+        <v>4.039209279529489</v>
       </c>
       <c r="N3" t="n">
-        <v>3.958176768501879</v>
+        <v>3.931710504819474</v>
       </c>
       <c r="O3" t="n">
         <v>2.623917660512988</v>
       </c>
       <c r="P3" t="n">
-        <v>0.264559894109861</v>
+        <v>0.2489660876757651</v>
       </c>
       <c r="Q3" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3.19844499586435</v>
+        <v>3.258610421836228</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2125</v>
+        <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8625</v>
+        <v>2.05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.199261542280325</v>
+        <v>3.259457223233494</v>
       </c>
       <c r="I4" t="n">
         <v>0.9875837281489953</v>
@@ -680,22 +680,22 @@
         <v>0.00326743996079072</v>
       </c>
       <c r="L4" t="n">
-        <v>3.857702989707564</v>
+        <v>3.987910472145074</v>
       </c>
       <c r="M4" t="n">
-        <v>3.817186734193759</v>
+        <v>3.851168109785983</v>
       </c>
       <c r="N4" t="n">
-        <v>3.559385721287371</v>
+        <v>3.586178728965855</v>
       </c>
       <c r="O4" t="n">
         <v>2.76409083483091</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4059553349875931</v>
+        <v>0.3655913978494624</v>
       </c>
       <c r="Q4" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.977698511166253</v>
+        <v>3.022140198511166</v>
       </c>
       <c r="F5" t="n">
-        <v>3.05</v>
+        <v>3.1375</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5325</v>
+        <v>1.5625</v>
       </c>
       <c r="H5" t="n">
-        <v>2.979575541949363</v>
+        <v>3.023862320039715</v>
       </c>
       <c r="I5" t="n">
         <v>0.9875837281489953</v>
@@ -741,22 +741,22 @@
         <v>0.004247671949027937</v>
       </c>
       <c r="L5" t="n">
-        <v>2.899852965201764</v>
+        <v>3.027936611664761</v>
       </c>
       <c r="M5" t="n">
-        <v>4.202908021565103</v>
+        <v>4.20764580950825</v>
       </c>
       <c r="N5" t="n">
-        <v>4.013396503839242</v>
+        <v>4.020421499754942</v>
       </c>
       <c r="O5" t="n">
         <v>2.42607417088711</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4775847808105873</v>
+        <v>0.4574028122415219</v>
       </c>
       <c r="Q5" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.425426991150442</v>
+        <v>3.481237631926121</v>
       </c>
       <c r="F6" t="n">
-        <v>3.425</v>
+        <v>3.4875</v>
       </c>
       <c r="G6" t="n">
-        <v>2.05</v>
+        <v>2.1625</v>
       </c>
       <c r="H6" t="n">
-        <v>3.425050902974504</v>
+        <v>3.480905641702408</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9230517889233786</v>
+        <v>0.9906877961117464</v>
       </c>
       <c r="J6" t="n">
         <v>0.2238196373141643</v>
@@ -802,22 +802,22 @@
         <v>0.000980231988237216</v>
       </c>
       <c r="L6" t="n">
-        <v>3.847247181833034</v>
+        <v>3.924358764907695</v>
       </c>
       <c r="M6" t="n">
-        <v>4.062408103251102</v>
+        <v>4.10913249469041</v>
       </c>
       <c r="N6" t="n">
-        <v>3.949191308609704</v>
+        <v>3.955726188531286</v>
       </c>
       <c r="O6" t="n">
         <v>3.139356314327724</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2766371681415929</v>
+        <v>0.2521437994722955</v>
       </c>
       <c r="Q6" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7">
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3.04028584708343</v>
+        <v>2.971229798812665</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0125</v>
+        <v>2.875</v>
       </c>
       <c r="G7" t="n">
-        <v>1.675</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>3.04028584708343</v>
+        <v>2.971348152424942</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7029897075641235</v>
+        <v>0.9906877961117464</v>
       </c>
       <c r="J7" t="n">
         <v>0.02728312367260251</v>
@@ -863,22 +863,22 @@
         <v>0.006044763927462833</v>
       </c>
       <c r="L7" t="n">
-        <v>2.901159941186081</v>
+        <v>3.070249959157</v>
       </c>
       <c r="M7" t="n">
-        <v>3.822251266132985</v>
+        <v>3.886293089364483</v>
       </c>
       <c r="N7" t="n">
-        <v>2.713608887436693</v>
+        <v>2.714262375428851</v>
       </c>
       <c r="O7" t="n">
         <v>3.529488645646136</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4924471299093656</v>
+        <v>0.5371042216358839</v>
       </c>
       <c r="Q7" t="n">
-        <v>215</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.649996820147545</v>
+        <v>2.588710009894459</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5625</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
         <v>1.45</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64978684143548</v>
+        <v>2.588615555922138</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6422153242934161</v>
+        <v>0.9906877961117464</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -924,22 +924,22 @@
         <v>0.00163371998039536</v>
       </c>
       <c r="L8" t="n">
-        <v>2.73256003920928</v>
+        <v>2.923868648913576</v>
       </c>
       <c r="M8" t="n">
-        <v>3.207155693514132</v>
+        <v>3.2888416925339</v>
       </c>
       <c r="N8" t="n">
-        <v>2.557915373305016</v>
+        <v>2.558568861297174</v>
       </c>
       <c r="O8" t="n">
         <v>2.840222185917334</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6761638259984737</v>
+        <v>0.7074538258575198</v>
       </c>
       <c r="Q8" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
